--- a/TomaInventarioWEB/Plantillas/Plantilla_Ubicacion.xlsx
+++ b/TomaInventarioWEB/Plantillas/Plantilla_Ubicacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Carlos Figueroa\Proyectos 2024\Toma Inventarios\Fuente\TomaInventario\TomaInventarioWEB\TomaInventarioWEB\Plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Desktop\Documentos\TomaDeInventario - Web\TomaInventario-GitHub\TomaInventarioWEB\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4CF3AB-7793-47E2-9F97-0DF3E291A701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6D0762-68E3-42A4-AC4E-66EC80D9ACFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>COD_ALMACEN</t>
-  </si>
-  <si>
-    <t>COD_UBICACION</t>
-  </si>
-  <si>
-    <t>DESC_UBICACION</t>
-  </si>
-  <si>
     <t>A1</t>
   </si>
   <si>
@@ -52,29 +43,25 @@
   </si>
   <si>
     <t>Ubicación</t>
+  </si>
+  <si>
+    <t>CÓDIGO DE ALMACEN</t>
+  </si>
+  <si>
+    <t>CÓDIGO DE UBICACIÓN</t>
+  </si>
+  <si>
+    <t>DESCRIPCIÓN DE UBICACIÓN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -86,6 +73,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -96,7 +90,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -126,15 +120,15 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,31 +446,31 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="68.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>5</v>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/TomaInventarioWEB/Plantillas/Plantilla_Ubicacion.xlsx
+++ b/TomaInventarioWEB/Plantillas/Plantilla_Ubicacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Desktop\Documentos\TomaDeInventario - Web\TomaInventario-GitHub\TomaInventarioWEB\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6D0762-68E3-42A4-AC4E-66EC80D9ACFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E20CBA-27F9-48F5-965E-B23B5E4120C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
+    <workbookView xWindow="2715" yWindow="2040" windowWidth="26085" windowHeight="14160" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -45,13 +45,13 @@
     <t>Ubicación</t>
   </si>
   <si>
-    <t>CÓDIGO DE ALMACEN</t>
-  </si>
-  <si>
-    <t>CÓDIGO DE UBICACIÓN</t>
-  </si>
-  <si>
-    <t>DESCRIPCIÓN DE UBICACIÓN</t>
+    <t>COD_ALMACEN</t>
+  </si>
+  <si>
+    <t>COD_UBICACION</t>
+  </si>
+  <si>
+    <t>DESC_UBICACION</t>
   </si>
 </sst>
 </file>

--- a/TomaInventarioWEB/Plantillas/Plantilla_Ubicacion.xlsx
+++ b/TomaInventarioWEB/Plantillas/Plantilla_Ubicacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Desktop\Documentos\TomaDeInventario - Web\TomaInventario-GitHub\TomaInventarioWEB\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E20CBA-27F9-48F5-965E-B23B5E4120C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610640A6-7A58-41A3-B922-075F519C9565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="2040" windowWidth="26085" windowHeight="14160" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -118,17 +118,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,24 +445,24 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.85546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
